--- a/Templates/water-quality-analysis/wqsample-sample-tracking-template.xlsx
+++ b/Templates/water-quality-analysis/wqsample-sample-tracking-template.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wampleka\Documents\Projects\WWS-data-management\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wampleka\Documents\Projects\WWS-standard-methods\Templates\water-quality-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDB93AC-28D3-4235-B773-0034D695E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B75C3C1-8BDB-4AE3-AE9B-A470673FC395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{92B9B79B-A9B6-48BE-A4FD-E6F212A8703B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92B9B79B-A9B6-48BE-A4FD-E6F212A8703B}"/>
   </bookViews>
   <sheets>
     <sheet name="date-1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'date-1'!$A$12:$I$204</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Sample Tracking Worksheet</t>
   </si>
@@ -281,11 +284,74 @@
         <b/>
         <i/>
         <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Description of where in the analysis process the sample is (ie. waiting to be analyzed, data collected, data QA/QC'ed)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Archieved </t>
+  </si>
+  <si>
+    <t>DOC01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used on 2-35 for degredation test. </t>
+  </si>
+  <si>
+    <t>Field Flags</t>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Field Flags</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Flags</t>
     </r>
     <r>
@@ -298,34 +364,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>: Note any major method deviations here (ie. analyzed out of hold times, missing samples) or other flag using standardized method codes (https://oregonstate.box.com/s/ygkfxbw7cvy7qb14vyr942jygq5uiznn). If no deviations put a "N"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Description of where in the analysis process the sample is (ie. waiting to be analyzed, data collected, data QA/QC'ed)</t>
     </r>
   </si>
 </sst>
@@ -333,7 +371,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,6 +450,12 @@
       <u/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -520,10 +564,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -551,27 +610,62 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -965,195 +1059,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B5CC33-0287-42C9-AD28-6A03CBC17BE3}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M117"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="50.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="57.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="G2" s="14" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="G3" s="14" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="10"/>
+      <c r="G3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="G4" s="14" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="G4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="G5" s="14" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="G5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="G6" s="14" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="G6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="G7" s="14" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="G7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="14" t="s">
+    <row r="8" spans="1:13" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E13" s="17"/>
+    </row>
+    <row r="117" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E117" s="17"/>
+      <c r="F117" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-    </row>
-    <row r="9" spans="1:13" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G10" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>12</v>
+      <c r="G117" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A12:I204" xr:uid="{18B5CC33-0287-42C9-AD28-6A03CBC17BE3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:H204">
+    <sortCondition ref="A13:A204"/>
+  </sortState>
   <mergeCells count="15">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
     <mergeCell ref="G10:M10"/>
     <mergeCell ref="G1:M1"/>
     <mergeCell ref="G2:M2"/>
@@ -1164,38 +1287,34 @@
     <mergeCell ref="G7:M7"/>
     <mergeCell ref="G8:M8"/>
     <mergeCell ref="G9:M9"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="B13:B1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>"Excess (Node 3)"</formula>
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>"Excess"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
-      <formula>"CCAL (Nutrients)"</formula>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"CCAL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"Shimadzu (DOC/TN)"</formula>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"Shimadzu"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"Aqualog (DOM)"</formula>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"Aqualog"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"BPCA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"SSC"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"Levoglucosan"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:B1048576" xr:uid="{8EDC692E-B8DF-4FCF-AC65-72478B5A6D4A}">
-      <formula1>" Aqualog (DOM), BPCA, CCAL (Nutrients), Excess (Node 3), Levoglucosan, Shimadzu (DOC/TN), SSC, Other (note in notes)"</formula1>
+      <formula1>" Aqualog, BPCA, CCAL, Excess, Levoglucosan, Shimadzu, SSC, Other (note in notes)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
